--- a/output/stock_quant_scores/VRTX_income_df.xlsx
+++ b/output/stock_quant_scores/VRTX_income_df.xlsx
@@ -1253,7 +1253,9 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>2791900000</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1264,7 +1266,9 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>9.09</v>
+      </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
         <v>0</v>
@@ -1273,7 +1277,9 @@
       <c r="Z6" t="n">
         <v>0</v>
       </c>
-      <c r="AA6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>2342100000</v>
+      </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
@@ -1296,9 +1302,13 @@
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>6670200000</v>
+      </c>
       <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>7574400000</v>
+      </c>
       <c r="AW6" t="inlineStr"/>
     </row>
   </sheetData>
